--- a/result.xlsx
+++ b/result.xlsx
@@ -1,114 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30015"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\【】理工大\【02】数学建模\2026\省赛出题\多源异质定位数据融合\更新\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DB44E1-A924-4996-81CE-10C837096C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
-  <si>
-    <t>目标编号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>任务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>注意：请按照时间先后顺序，依次在表格中填写相关内容。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>填写范例：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P01</t>
-  </si>
-  <si>
-    <t>拍照</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>开始准备时刻(s)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>任务执行时刻(s)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color rgb="FFFF0000"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -126,24 +76,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -409,129 +418,283 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" customWidth="1"/>
-    <col min="11" max="11" width="14.77734375" customWidth="1"/>
-    <col min="12" max="12" width="16.5546875" customWidth="1"/>
+    <col width="15.77734375" customWidth="1" min="4" max="4"/>
+    <col width="16.44140625" customWidth="1" min="5" max="5"/>
+    <col width="14.77734375" customWidth="1" min="11" max="11"/>
+    <col width="16.5546875" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>目标编号</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>任务</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>开始准备时刻(s)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>任务执行时刻(s)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>注意：请按照时间先后顺序，依次在表格中填写相关内容。</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>填写范例：</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>目标编号</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>任务</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>开始准备时刻(s)</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>任务执行时刻(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>3.05</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>279.2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>279.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K4" s="2">
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="L4" s="2">
-        <v>3.05</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>282.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>282.9</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/result.xlsx
+++ b/result.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -474,7 +474,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
         <v>25.5</v>
       </c>
       <c r="E2" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="E3" t="n">
         <v>26.7</v>
@@ -562,7 +562,7 @@
         <v>38.3</v>
       </c>
       <c r="E4" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1</v>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="E5" t="n">
         <v>42</v>
@@ -616,7 +616,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -628,7 +628,7 @@
         <v>46.9</v>
       </c>
       <c r="E6" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="7">
@@ -637,7 +637,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -646,54 +646,14 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="E7" t="n">
         <v>50.9</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>P05</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>拍照</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>279.2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>279.6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>拍照</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>282.5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>282.9</v>
-      </c>
-    </row>
+    <row r="8"/>
+    <row r="9"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
